--- a/data/trans_orig/IP19C08-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP19C08-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49145</t>
+          <t>48329</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54162</t>
+          <t>54166</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45147</t>
+          <t>44542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96361</t>
+          <t>96157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102815</t>
+          <t>102786</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34881</t>
+          <t>34671</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39879</t>
+          <t>39880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31099</t>
+          <t>30785</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36392</t>
+          <t>36414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68709</t>
+          <t>68116</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75517</t>
+          <t>75422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32075</t>
+          <t>32237</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46858</t>
+          <t>47313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52565</t>
+          <t>52687</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81211</t>
+          <t>80583</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87157</t>
+          <t>87211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11435</t>
+          <t>11389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86702</t>
+          <t>86748</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94450</t>
+          <t>94352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90286</t>
+          <t>90238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95551</t>
+          <t>95518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179411</t>
+          <t>179363</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>188590</t>
+          <t>188601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>14029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44705</t>
+          <t>44617</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52305</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62711</t>
+          <t>62647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69231</t>
+          <t>69227</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>110768</t>
+          <t>110664</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120464</t>
+          <t>120063</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34447</t>
+          <t>34410</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27555</t>
+          <t>27678</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33830</t>
+          <t>34280</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64784</t>
+          <t>65242</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72996</t>
+          <t>72931</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>12772</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27292</t>
+          <t>27283</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23512</t>
+          <t>23315</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>26408</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45450</t>
+          <t>45472</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>295806</t>
+          <t>295815</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>310101</t>
+          <t>310326</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>318176</t>
+          <t>318373</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330638</t>
+          <t>330775</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>619336</t>
+          <t>619314</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>638788</t>
+          <t>638378</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>722</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40092</t>
+          <t>40184</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46833</t>
+          <t>46868</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34981</t>
+          <t>35413</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40156</t>
+          <t>40162</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78454</t>
+          <t>78298</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86197</t>
+          <t>86305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42966</t>
+          <t>43018</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47789</t>
+          <t>47694</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52414</t>
+          <t>52415</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93320</t>
+          <t>93366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99265</t>
+          <t>99898</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>682</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7183</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35517</t>
+          <t>35399</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41040</t>
+          <t>41043</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36575</t>
+          <t>36515</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74334</t>
+          <t>74058</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80203</t>
+          <t>80201</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9013</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12327</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84788</t>
+          <t>84522</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90594</t>
+          <t>90601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88953</t>
+          <t>89205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96472</t>
+          <t>96489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>176868</t>
+          <t>176981</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>185901</t>
+          <t>185764</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>707</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12360</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75444</t>
+          <t>76009</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81525</t>
+          <t>81521</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65616</t>
+          <t>65403</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72296</t>
+          <t>72267</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143535</t>
+          <t>144113</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152527</t>
+          <t>152464</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21431</t>
+          <t>21972</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34375</t>
+          <t>33985</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58398</t>
+          <t>58298</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,44 +5441,44 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5,87%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>13790</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>8791</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>20349</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>2,56%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>13790</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>8242</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>20343</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
           <t>5,93%</t>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19975</t>
+          <t>18876</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36736</t>
+          <t>36497</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>315962</t>
+          <t>316835</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>327984</t>
+          <t>328122</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,49 +5554,49 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>97,48%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>329109</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>322550</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>334108</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>94,07%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>97,44%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>329109</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>322556</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>334657</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>94,07%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>934</t>
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>642768</t>
+          <t>643007</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>659529</t>
+          <t>660628</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46494</t>
+          <t>44580</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89952</t>
+          <t>89472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48903</t>
+          <t>49099</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55074</t>
+          <t>55077</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50484</t>
+          <t>51068</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102320</t>
+          <t>101624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108676</t>
+          <t>109082</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30065</t>
+          <t>30124</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60347</t>
+          <t>61078</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10737</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19416</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99774</t>
+          <t>100247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107899</t>
+          <t>108129</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92278</t>
+          <t>92440</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100340</t>
+          <t>100337</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>194699</t>
+          <t>195260</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>206784</t>
+          <t>206597</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61712</t>
+          <t>61871</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67941</t>
+          <t>68127</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70070</t>
+          <t>70219</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>134037</t>
+          <t>133990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>141034</t>
+          <t>141133</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>586</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28251</t>
+          <t>28352</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28524</t>
+          <t>28898</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>59661</t>
+          <t>59735</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>64208</t>
+          <t>64204</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20401</t>
+          <t>20068</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,47 +8111,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>22945</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>16062</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>30873</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>4,47%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>22945</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>16192</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>32286</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>322342</t>
+          <t>322675</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>334614</t>
+          <t>334776</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>332103</t>
+          <t>332204</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>342246</t>
+          <t>342697</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,47 +8224,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>95,56%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>667429</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>659501</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>674312</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>96,68%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>95,53%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>667429</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>658088</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>674182</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>96,68%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11787</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66297</t>
+          <t>66232</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85012</t>
+          <t>84303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94084</t>
+          <t>93734</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154531</t>
+          <t>154391</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>164950</t>
+          <t>165008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56848</t>
+          <t>57320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62105</t>
+          <t>62077</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66897</t>
+          <t>67873</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127608</t>
+          <t>127040</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133136</t>
+          <t>133098</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25162</t>
+          <t>25361</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31530</t>
+          <t>31430</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58097</t>
+          <t>58568</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63505</t>
+          <t>63512</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23168</t>
+          <t>23695</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28983</t>
+          <t>24187</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103712</t>
+          <t>103909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>110280</t>
+          <t>110259</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104225</t>
+          <t>103698</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>125501</t>
+          <t>125579</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>209456</t>
+          <t>214252</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>234667</t>
+          <t>234679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>5964</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63760</t>
+          <t>63283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99307</t>
+          <t>99610</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>165601</t>
+          <t>165734</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>170989</t>
+          <t>171033</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40813</t>
+          <t>39884</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85631</t>
+          <t>85738</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>14854</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31810</t>
+          <t>32267</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16694</t>
+          <t>16414</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40731</t>
+          <t>41248</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>372171</t>
+          <t>371959</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>382202</t>
+          <t>382150</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>446855</t>
+          <t>446398</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>469757</t>
+          <t>469622</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>824747</t>
+          <t>824230</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>848784</t>
+          <t>849064</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
